--- a/circle_details.xlsx
+++ b/circle_details.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Circle_Details" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G358"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,14 +435,8 @@
       <c r="D2" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2">
         <v>586209</v>
-      </c>
-      <c r="F2" t="str">
-        <v>ಸಂಗಮೇಶ ಕುಂಬಾರ</v>
-      </c>
-      <c r="G2" t="str">
-        <v>9845011221</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +444,7 @@
         <v>ಅಗಸನಾಳ</v>
       </c>
       <c r="B3" t="str">
-        <v>ಧೋಳಖೇಡ ಸರ್ಕಲ</v>
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
       </c>
       <c r="C3" t="str">
         <v>ಚಡಚಣ</v>
@@ -458,22 +452,16 @@
       <c r="D3" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3">
         <v>586207</v>
-      </c>
-      <c r="F3" t="str">
-        <v>ರಮೇಶ ಪಾಟೀಲ</v>
-      </c>
-      <c r="G3" t="str">
-        <v>9845011222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ಅಂಜುಟಗಿ</v>
+        <v>ಅಂಜುಟಿಗಿ</v>
       </c>
       <c r="B4" t="str">
-        <v>ಇಂಡಿ ಸ್ಟೇಶನ್ ಸರ್ಕಲ</v>
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
       </c>
       <c r="C4" t="str">
         <v>ಇಂಡಿ</v>
@@ -481,14 +469,8 @@
       <c r="D4" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4">
         <v>586209</v>
-      </c>
-      <c r="F4" t="str">
-        <v>ಸುರೇಶ ಬಿರಾದಾರ</v>
-      </c>
-      <c r="G4" t="str">
-        <v>9845011223</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +478,7 @@
         <v>ಅಣಚಿ</v>
       </c>
       <c r="B5" t="str">
-        <v>ಧೋಳಖೇಡ ಸರ್ಕಲ</v>
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
       </c>
       <c r="C5" t="str">
         <v>ಚಡಚಣ</v>
@@ -504,14 +486,8 @@
       <c r="D5" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5">
         <v>586207</v>
-      </c>
-      <c r="F5" t="str">
-        <v>ರಮೇಶ ಪಾಟೀಲ</v>
-      </c>
-      <c r="G5" t="str">
-        <v>9845011222</v>
       </c>
     </row>
     <row r="6">
@@ -527,37 +503,13 @@
       <c r="D6" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E6" t="str">
-        <v>586112</v>
-      </c>
-      <c r="F6" t="str">
-        <v>ಬಸವರಾಜ ಹಡಪದ</v>
-      </c>
-      <c r="G6" t="str">
-        <v>9845011224</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ಅಫಜಲಪೂರ</v>
+        <v>ಅಪಜಲಪೂರ</v>
       </c>
       <c r="B7" t="str">
         <v>Post</v>
-      </c>
-      <c r="C7" t="str">
-        <v>III</v>
-      </c>
-      <c r="D7" t="str">
-        <v>ಕಲಬುರಗಿ</v>
-      </c>
-      <c r="E7" t="str">
-        <v>598999</v>
-      </c>
-      <c r="F7" t="str">
-        <v>ಪೋಸ್ಟ್ ಅಧಿಕಾರಿ</v>
-      </c>
-      <c r="G7" t="str">
-        <v>9845011225</v>
       </c>
     </row>
     <row r="8">
@@ -567,28 +519,13 @@
       <c r="B8" t="str">
         <v>Post</v>
       </c>
-      <c r="C8" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="D8" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E8" t="str">
-        <v>586104</v>
-      </c>
-      <c r="F8" t="str">
-        <v>ಪೋಸ್ಟ್ ಅಧಿಕಾರಿ</v>
-      </c>
-      <c r="G8" t="str">
-        <v>9845011225</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>ಅರ್ಜನಾಳ</v>
       </c>
       <c r="B9" t="str">
-        <v>ಧೋಳಖೇಡ ಸರ್ಕಲ</v>
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
       </c>
       <c r="C9" t="str">
         <v>ಚಡಚಣ</v>
@@ -596,14 +533,8 @@
       <c r="D9" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9">
         <v>586207</v>
-      </c>
-      <c r="F9" t="str">
-        <v>ರಮೇಶ ಪಾಟೀಲ</v>
-      </c>
-      <c r="G9" t="str">
-        <v>9845011222</v>
       </c>
     </row>
     <row r="10">
@@ -619,14 +550,8 @@
       <c r="D10" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10">
         <v>586217</v>
-      </c>
-      <c r="F10" t="str">
-        <v>ಮಲ್ಲಪ್ಪ ಪೂಜಾರಿ</v>
-      </c>
-      <c r="G10" t="str">
-        <v>9845011226</v>
       </c>
     </row>
     <row r="11">
@@ -642,14 +567,8 @@
       <c r="D11" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11">
         <v>586217</v>
-      </c>
-      <c r="F11" t="str">
-        <v>ಮಲ್ಲಪ್ಪ ಪೂಜಾರಿ</v>
-      </c>
-      <c r="G11" t="str">
-        <v>9845011226</v>
       </c>
     </row>
     <row r="12">
@@ -659,21 +578,6 @@
       <c r="B12" t="str">
         <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
       </c>
-      <c r="C12" t="str">
-        <v>ಸಿಂದಗಿ</v>
-      </c>
-      <c r="D12" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E12" t="str">
-        <v>586128</v>
-      </c>
-      <c r="F12" t="str">
-        <v>ಸಿದ್ದರಾಮಯ್ಯ ಹಿರೇಮಠ</v>
-      </c>
-      <c r="G12" t="str">
-        <v>9845011227</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -682,21 +586,6 @@
       <c r="B13" t="str">
         <v>Post</v>
       </c>
-      <c r="C13" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="D13" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E13" t="str">
-        <v>586101</v>
-      </c>
-      <c r="F13" t="str">
-        <v>ಪೋಸ್ಟ್ ಅಧಿಕಾರಿ</v>
-      </c>
-      <c r="G13" t="str">
-        <v>9845011225</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -705,43 +594,13 @@
       <c r="B14" t="str">
         <v>Post</v>
       </c>
-      <c r="C14" t="str">
-        <v>ಇಂಡಿ</v>
-      </c>
-      <c r="D14" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E14" t="str">
-        <v>586209</v>
-      </c>
-      <c r="F14" t="str">
-        <v>ಪೋಸ್ಟ್ ಅಧಿಕಾರಿ</v>
-      </c>
-      <c r="G14" t="str">
-        <v>9845011225</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ಅಸ್ತಿ</v>
+        <v>ಅಸ್ಕಿ</v>
       </c>
       <c r="B15" t="str">
         <v>Post</v>
-      </c>
-      <c r="C15" t="str">
-        <v>ಇಂಡಿ</v>
-      </c>
-      <c r="D15" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E15" t="str">
-        <v>586209</v>
-      </c>
-      <c r="F15" t="str">
-        <v>ಪೋಸ್ಟ್ ಅಧಿಕಾರಿ</v>
-      </c>
-      <c r="G15" t="str">
-        <v>9845011225</v>
       </c>
     </row>
     <row r="16">
@@ -749,7 +608,7 @@
         <v>ಅಹೀರಸಂಗ</v>
       </c>
       <c r="B16" t="str">
-        <v>ಇಂಡಿ ಸ್ಟೇಶನ್ ಸರ್ಕಲ</v>
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
       </c>
       <c r="C16" t="str">
         <v>ಇಂಡಿ</v>
@@ -757,14 +616,8 @@
       <c r="D16" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16">
         <v>586209</v>
-      </c>
-      <c r="F16" t="str">
-        <v>ಸುರೇಶ ಬಿರಾದಾರ</v>
-      </c>
-      <c r="G16" t="str">
-        <v>9845011223</v>
       </c>
     </row>
     <row r="17">
@@ -774,21 +627,6 @@
       <c r="B17" t="str">
         <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
       </c>
-      <c r="C17" t="str">
-        <v>ಸಿಂದಗಿ</v>
-      </c>
-      <c r="D17" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E17" t="str">
-        <v>586128</v>
-      </c>
-      <c r="F17" t="str">
-        <v>ಸಿದ್ದರಾಮಯ್ಯ ಹಿರೇಮಠ</v>
-      </c>
-      <c r="G17" t="str">
-        <v>9845011227</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -797,21 +635,6 @@
       <c r="B18" t="str">
         <v>Post</v>
       </c>
-      <c r="C18" t="str">
-        <v>ನಿಡಗುಂದಿ</v>
-      </c>
-      <c r="D18" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E18" t="str">
-        <v>586201</v>
-      </c>
-      <c r="F18" t="str">
-        <v>ಪೋಸ್ಟ್ ಅಧಿಕಾರಿ</v>
-      </c>
-      <c r="G18" t="str">
-        <v>9845011225</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -820,71 +643,26 @@
       <c r="B19" t="str">
         <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
       </c>
-      <c r="C19" t="str">
-        <v>ಸಿಂದಗಿ</v>
-      </c>
-      <c r="D19" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E19" t="str">
-        <v>586202</v>
-      </c>
-      <c r="F19" t="str">
-        <v>ಸಿದ್ದರಾಮಯ್ಯ ಹಿರೇಮಠ</v>
-      </c>
-      <c r="G19" t="str">
-        <v>9845011227</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ಅಸಂಗಿಹಾಳ</v>
+        <v>ಆಸಂಗಿಹಾಳ</v>
       </c>
       <c r="B20" t="str">
         <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
-      </c>
-      <c r="C20" t="str">
-        <v>ಸಿಂದಗಿ</v>
-      </c>
-      <c r="D20" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E20" t="str">
-        <v>586128</v>
-      </c>
-      <c r="F20" t="str">
-        <v>ಸಿದ್ದರಾಮಯ್ಯ ಹಿರೇಮಠ</v>
-      </c>
-      <c r="G20" t="str">
-        <v>9845011227</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ಬಳ್ಳೊಳ್ಳಿ</v>
+        <v>ಆಹೇರಿ</v>
       </c>
       <c r="B21" t="str">
-        <v>ಬಳ್ಳೊಳ್ಳಿ ಸರ್ಕಲ</v>
-      </c>
-      <c r="C21" t="str">
-        <v>ಇಂಡಿ</v>
-      </c>
-      <c r="D21" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E21" t="str">
-        <v>586117</v>
-      </c>
-      <c r="F21" t="str">
-        <v>ಮಲ್ಲಪ್ಪ ಗೌಡರ</v>
-      </c>
-      <c r="G21" t="str">
-        <v>9845011228</v>
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ಜೇವೂರ</v>
+        <v>ಆಳೂರ</v>
       </c>
       <c r="B22" t="str">
         <v>ಇಂಡಿ ಸರ್ಕಲ</v>
@@ -895,45 +673,33 @@
       <c r="D22" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E22" t="str">
-        <v>586112</v>
-      </c>
-      <c r="F22" t="str">
-        <v>ಸಂಗಮೇಶ ಕುಂಬಾರ</v>
-      </c>
-      <c r="G22" t="str">
-        <v>9845011221</v>
+      <c r="E22">
+        <v>586209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ಚಡಚಣ</v>
+        <v>ಆಳೂರ ಎಲ್ ಟಿ</v>
       </c>
       <c r="B23" t="str">
-        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
       </c>
       <c r="C23" t="str">
-        <v>ಚಡಚಣ</v>
+        <v>ಇಂಡಿ</v>
       </c>
       <c r="D23" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E23" t="str">
-        <v>586205</v>
-      </c>
-      <c r="F23" t="str">
-        <v>ಆನಂದ ಬಿರಾದಾರ</v>
-      </c>
-      <c r="G23" t="str">
-        <v>9845011229</v>
+      <c r="E23">
+        <v>586209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ಹೊರ್ತಿ</v>
+        <v>ಇಂಗಳಗಿ</v>
       </c>
       <c r="B24" t="str">
-        <v>ಹೊರ್ತಿ ಸರ್ಕಲ</v>
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
       </c>
       <c r="C24" t="str">
         <v>ಇಂಡಿ</v>
@@ -941,88 +707,3882 @@
       <c r="D24" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E24" t="str">
-        <v>586117</v>
-      </c>
-      <c r="F24" t="str">
-        <v>ಪ್ರಕಾಶ ಕಲಬುರಗಿ</v>
-      </c>
-      <c r="G24" t="str">
-        <v>9845011230</v>
+      <c r="E24">
+        <v>586209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ಲಚ್ಯಾಣ</v>
+        <v>ಇಂಗಳಗಿ ಬಿ ಬಿ</v>
       </c>
       <c r="B25" t="str">
-        <v>ಲಚ್ಯಾಣ ಸರ್ಕಲ</v>
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
       </c>
       <c r="C25" t="str">
         <v>ಇಂಡಿ</v>
       </c>
       <c r="D25" t="str">
         <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E25" t="str">
-        <v>586211</v>
-      </c>
-      <c r="F25" t="str">
-        <v>ವಿಜಯಕುಮಾರ ಪಾಟೀಲ</v>
-      </c>
-      <c r="G25" t="str">
-        <v>9845011231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ಸಾಲೋಟಗಿ</v>
+        <v>ಇಂಚಗೇರಿ</v>
       </c>
       <c r="B26" t="str">
-        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
       </c>
       <c r="C26" t="str">
-        <v>ಇಂಡಿ</v>
+        <v>ಚಡಚಣ</v>
       </c>
       <c r="D26" t="str">
         <v>ವಿಜಯಪುರ</v>
       </c>
-      <c r="E26" t="str">
-        <v>586217</v>
-      </c>
-      <c r="F26" t="str">
-        <v>ಮಲ್ಲಪ್ಪ ಪೂಜಾರಿ</v>
-      </c>
-      <c r="G26" t="str">
-        <v>9845011226</v>
+      <c r="E26">
+        <v>586204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v>ಇಂಚಗೇರಿ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B27" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C27" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D27" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E27">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>ಇಟಗಿ</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="B29" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E29">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>ಇಂಡಿ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B30" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C30" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D30" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E30">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>ಇಂಡಿ ಡಿಗಿಭಾವಿ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B31" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C31" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D31" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E31">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>ಇಂಡಿ ಮಧುರನಗರ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B32" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D32" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E32">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>ಇಂಡಿ ರೇಲ್ವೆಸ್ಟೆಶನ್</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D33" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E33">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>ಇಬ್ರಾಹಿಂಪೂರ</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>ಇಲಕಲ್</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>ಉಕ್ಕಲಿ</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>ಉಚಿತನಾವದಗಿ</v>
+      </c>
+      <c r="B37" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>ಉಮರಜ</v>
+      </c>
+      <c r="B38" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D38" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E38">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>ಉಮರಾಣಿ</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D39" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>ಏಳಗಿ</v>
+      </c>
+      <c r="B40" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C40" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D40" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E40">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>ಏಳಗಿ ಪಿ ಹೆಚ್</v>
+      </c>
+      <c r="B41" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C41" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D41" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E41">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ಓತಿಹಾಳ</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D42" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>ಕಕ್ಕಳಮೇಲಿ</v>
+      </c>
+      <c r="B43" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>ಕಗ್ಗೋಡ</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>ಕಂಚನಾಳ</v>
+      </c>
+      <c r="B45" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C45" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D45" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>ಕಡಕೋಳ</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>ಕಡಣಿ</v>
+      </c>
+      <c r="B47" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>ಕಡ್ಲೆವಾಡ</v>
+      </c>
+      <c r="B48" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C48" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D48" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>ಕಡ್ಲೆವಾಡ ಪಿಎ</v>
+      </c>
+      <c r="B49" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C49" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D49" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>ಕಣ್ಣ ಗುಡ್ಡಿಹಾಳ</v>
+      </c>
+      <c r="B50" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>ಕಥೇವಾಡ</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>ಕನಕನಾಳ</v>
+      </c>
+      <c r="B52" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C52" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D52" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E52">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>ಕನಮಡಿ</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>ಕನ್ನೂರ</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>ಕನ್ನೋಳ್ಳಿ</v>
+      </c>
+      <c r="B55" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>ಕಪನಿಂಬರಗಿ</v>
+      </c>
+      <c r="B56" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C56" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D56" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E56">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>ಕರವಿನಾಳ</v>
+      </c>
+      <c r="B57" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>ಕರೂಟಗಿ</v>
+      </c>
+      <c r="B58" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>ಕಲಕೇರಿ</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>ಕಲಹಳ್ಳಿ</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>ಕಾಖಂಡಕಿ</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>ಕಾತ್ರಾಳ</v>
+      </c>
+      <c r="B62" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C62" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D62" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E62">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ಕಿಲಾಡೋಣ</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ಕುಬಕಡ್ಡಿ</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>ಕುಮಟೆ</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>ಕುಮಶಿ</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>ಕುಮಸಗಿ</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>ಕುರಬತ್ತಳ್ಳಿ</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>ಕುಳೇಕುಮಟಗಿ</v>
+      </c>
+      <c r="B69" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>ಕೂಡಗಿ</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C70" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D70" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E70">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>ಕೂಡಗಿ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C71" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D71" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E71">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>ಕೆಂಗನಾಳ</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C72" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D72" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>ಕೆರುಟಗಿ</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>ಕೆರುಟಗಿ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C75" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D75" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>ಕೆಸರಟ್ಟಿ</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>ಕೆಸರಾಳ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B77" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>ಕೆಸರಾಳ ತಾಂಡಾ</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>ಕೊಕಟನೂರ</v>
+      </c>
+      <c r="B79" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>ಕೊಂಕಣಗಾಂವ</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C80" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D80" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E80">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>ಕೊಟ್ನಾಳ</v>
+      </c>
+      <c r="B81" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C81" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D81" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E81">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>ಕೊಟ್ಯಾಳ</v>
+      </c>
+      <c r="B82" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C82" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D82" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E82">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>ಕೊಂಡಗೂಳಿ</v>
+      </c>
+      <c r="B83" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>ಕೊಲ್ಹಾರ</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>ಕೊಳೂರಗಿ</v>
+      </c>
+      <c r="B85" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C85" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D85" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E85">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>ಕೋರವಾರ</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>ಕೋರಳ್ಳಿ</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>ಕೋರೆಗಾಂವ</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>ಕ್ಯಾತನಕೇರಿ</v>
+      </c>
+      <c r="B89" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C89" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D89" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E89">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>ಖಾನಾಪೂರ</v>
+      </c>
+      <c r="B90" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>ಖೇಡಗಿ</v>
+      </c>
+      <c r="B91" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C91" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D91" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E91">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>ಖೈನೂರ</v>
+      </c>
+      <c r="B92" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>ಗಂಗನಳ್ಳಿ</v>
+      </c>
+      <c r="B93" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C93" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D93" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>ಗಣವಲಗಾ</v>
+      </c>
+      <c r="B94" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C94" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D94" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>ಗಣಿಹಾರ</v>
+      </c>
+      <c r="B95" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>ಗದ್ಯಾಳ</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>ಗಬಸಾವಳಗಿ</v>
+      </c>
+      <c r="B97" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>ಗುಡ್ಡಳ್ಳಿ</v>
+      </c>
+      <c r="B98" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>ಗುಣಕಿ</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>ಗುತ್ತರಗಿ</v>
+      </c>
+      <c r="B100" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>ಗುಂದಗಿ</v>
+      </c>
+      <c r="B101" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>ಗುಂದವಾನ</v>
+      </c>
+      <c r="B102" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D102" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E102">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>ಗುಬ್ಬೇವಾಡ</v>
+      </c>
+      <c r="B103" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D103" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E103">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>ಗುಲಬರ್ಗಾ</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>ಗುಳೇದಗುಡ್ಡ</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>ಗೊರನಾಳ</v>
+      </c>
+      <c r="B106" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C106" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D106" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>ಗೊರವಗುಂಡಗಿ</v>
+      </c>
+      <c r="B107" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>ಗೊಲಗೇರಿ</v>
+      </c>
+      <c r="B108" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>ಗೊಳಸಾರ</v>
+      </c>
+      <c r="B109" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C109" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D109" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E109">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>ಗೋಟ್ಯಾಳ</v>
+      </c>
+      <c r="B110" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C110" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D110" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E110">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>ಗೋಡಿಹಾಳ</v>
+      </c>
+      <c r="B111" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C111" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D111" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>ಗೋರನಾಳ</v>
+      </c>
+      <c r="B112" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C112" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D112" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>ಗೋಲಗೆರಿ</v>
+      </c>
+      <c r="B113" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>ಗೋವಿಂದಪೂರ</v>
+      </c>
+      <c r="B114" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C114" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D114" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E114">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>ಗೋಳಸಾರ</v>
+      </c>
+      <c r="B115" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C115" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D115" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E115">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>ಘತ್ತರಗಿ</v>
+      </c>
+      <c r="B116" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>ಚಟ್ಟರಕಿ</v>
+      </c>
+      <c r="B117" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C117" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D117" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>ಚಟ್ನಳ್ಳಿ</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="B119" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C119" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D119" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E119">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>ಚಣೇಗಾಂವ</v>
+      </c>
+      <c r="B120" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C120" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D120" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E120">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>ಚವಡಿಹಾಳ</v>
+      </c>
+      <c r="B121" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C121" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D121" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E121">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>ಚಾಂದಕವಟೆ</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>ಚಿಕ್ಕಬೇವನೂರ</v>
+      </c>
+      <c r="B123" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C123" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D123" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E123">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>ಚಿಕ್ಕಮಣ್ಣೂರ</v>
+      </c>
+      <c r="B124" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C124" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D124" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E124">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>ಚಿಕ್ಕರೂಗಿ</v>
+      </c>
+      <c r="B125" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C125" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D125" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>ಚಿಕ್ಕಸಿಂದಗಿ</v>
+      </c>
+      <c r="B126" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>ಚಿಮ್ಮಡ</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>ಚೋರಗಿ</v>
+      </c>
+      <c r="B128" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C128" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D128" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E128">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>ಜಂಬಗಿ</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>ಜಮಖಂಡಿ</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>ಜಾಲವಾದ</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C131" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D131" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>ಜಿಗಜೀವಣಗಿ</v>
+      </c>
+      <c r="B132" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C132" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D132" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E132">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>ಜೀರಂಕಲಗಿ</v>
+      </c>
+      <c r="B133" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C133" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D133" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E133">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ಜೇವೂರ</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C134" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D134" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E134">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>ಝಳಕಿ</v>
+      </c>
+      <c r="B135" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C135" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D135" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E135">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>ಟಾಕಳಿ</v>
+      </c>
+      <c r="B136" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C136" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D136" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>ಡಂಬಳ</v>
+      </c>
+      <c r="B137" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>ಢವಳಾರ</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>ತಂಗಡಗಿ</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>ತಡವಲಗಾ</v>
+      </c>
+      <c r="B140" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C140" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D140" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>ತದ್ದೇವಾಡಿ</v>
+      </c>
+      <c r="B141" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C141" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D141" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>ತಳೆವಾಡ</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>ತಾಂಬಾ</v>
+      </c>
+      <c r="B143" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C143" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D143" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>ತಾಂಬಾ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B144" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C144" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D144" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>ತಾರಾಪೂರ</v>
+      </c>
+      <c r="B145" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>ತಾವರಖೇಡ</v>
+      </c>
+      <c r="B146" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>ತಾವರಗೇರಿ</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>ತಾಳಿಕೋಟ</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>ತಿಕೋಟಾ</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>ತಿಡಗುಂದಿ</v>
+      </c>
+      <c r="B150" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C150" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D150" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E150">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>ತುಮಕೂರ</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>ತುರನಕೇರಿ</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>ತೆಗ್ಗಿಹಳ್ಳಿ</v>
+      </c>
+      <c r="B153" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C153" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D153" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E153">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>ತೆನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B154" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C154" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D154" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>ತೇರದಾಳ</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>ದಸೂರ</v>
+      </c>
+      <c r="B156" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C156" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D156" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E156">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>ದಾವಣಗೇರೆ</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>ದಿಂಡವಾರ</v>
+      </c>
+      <c r="B158" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C158" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D158" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>ದೆಗಿನಾಳ</v>
+      </c>
+      <c r="B159" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C159" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D159" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E159">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>ದೇವಣಗಾಂವ</v>
+      </c>
+      <c r="B160" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>ದೇವರಗೆಣ್ಣೂರ</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>ದೇವರನಾವದಗಿ</v>
+      </c>
+      <c r="B162" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>ದೇವರನಿಂಬರಗಿ</v>
+      </c>
+      <c r="B163" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C163" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D163" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E163">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+      <c r="B164" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C164" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D164" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>ದೇವೂರ</v>
+      </c>
+      <c r="B165" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C165" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D165" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>ದೇಸುಣಗಿ</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>ಧಾರವಾಡ</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>ಧುಮಕನಾಳ</v>
+      </c>
+      <c r="B168" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C168" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D168" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E168">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>ಧೂಳಖೇಡ</v>
+      </c>
+      <c r="B169" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C169" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D169" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E169">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>ನಂದಗಾಂವ</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>ನಂದಗೇರಿ</v>
+      </c>
+      <c r="B171" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>ನಂದರಗಿ</v>
+      </c>
+      <c r="B172" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C172" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D172" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E172">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>ನಂದ್ರಾಳ</v>
+      </c>
+      <c r="B173" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C173" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D173" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E173">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>ನಾಗಠಾಣ</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>ನಾಗನೂರ</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>ನಾಗರಹಳ್ಳಿ</v>
+      </c>
+      <c r="B176" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>ನಾಗಾಂವಿ</v>
+      </c>
+      <c r="B177" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>ನಾಗಾಂವಿ ಕೆ ಡಿ</v>
+      </c>
+      <c r="B178" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>ನಾಗಾಂವಿ ಬಿ ಕೆ</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>ನಾದ ಕೆ ಡಿ</v>
+      </c>
+      <c r="B180" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C180" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D180" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E180">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>ನಾದ ಬಿ ಕೆ</v>
+      </c>
+      <c r="B181" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C181" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D181" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E181">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>ನಾಲತವಾಡ</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>ನಾವದಗಿ</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>ನಿಡಗುಂದಿ</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>ನಿಂಬರಗಿ</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>ನಿಂಬಾಳ ಕೆ ಡಿ</v>
+      </c>
+      <c r="B186" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C186" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D186" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E186">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>ನಿಂಬಾಳ ಬಿ ಕೆ</v>
+      </c>
+      <c r="B187" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C187" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D187" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E187">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>ನಿವಾಳಖೇಡ</v>
+      </c>
+      <c r="B188" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C188" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D188" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>ನೀರಲಗಿ</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>ನೀವರಗಿ</v>
+      </c>
+      <c r="B190" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C190" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D190" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E190">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>ಪಡಗಾನೂರ</v>
+      </c>
+      <c r="B191" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C191" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D191" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>ಪಡನೂರ</v>
+      </c>
+      <c r="B192" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C192" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D192" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E192">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>ಪುರದಾಳ</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>ಬಂಕಲಗಿ</v>
+      </c>
+      <c r="B194" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>ಬಗಲೂರ</v>
+      </c>
+      <c r="B195" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>ಬಟಗೇರಿ</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>ಬಂಟನೂರ</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>ಬಂಥನಾಳ</v>
+      </c>
+      <c r="B198" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C198" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D198" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>ಬಂದಾಳ</v>
+      </c>
+      <c r="B199" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>ಬನ್ನಟ್ಟಿ ಪಿ ಟಿ</v>
+      </c>
+      <c r="B200" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>ಬನ್ನಹಟ್ಟಿ</v>
+      </c>
+      <c r="B201" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C201" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D201" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>ಬಬಲಾದ</v>
+      </c>
+      <c r="B202" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C202" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D202" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E202">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>ಬಬಲೇಶ್ವರ</v>
+      </c>
+      <c r="B203" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>ಬಮ್ಮನಜೋಗಿ</v>
+      </c>
+      <c r="B204" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>ಬಮ್ಮನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B205" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>ಬರಗುಡಿ</v>
+      </c>
+      <c r="B206" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C206" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D206" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E206">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>ಬರಟಗಿ</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>ಬರಡೋಲ</v>
+      </c>
+      <c r="B208" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C208" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D208" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E208">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>ಬರೂರ</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>ಬಸನಾಳ</v>
+      </c>
+      <c r="B210" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C210" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D210" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E210">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>ಬಸವನ ಬಾಗೇವಾಡಿ</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>ಬಸವನಹಟ್ಟಿ</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>ಬಳಗಾನೂರ</v>
+      </c>
+      <c r="B213" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>ಬಳುಂಡಗಿ</v>
+      </c>
+      <c r="B214" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>ಬಳ್ಳೊಳ್ಳಿ</v>
+      </c>
+      <c r="B215" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C215" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D215" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E215">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>ಬಾಗಲಕೋಟ</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>ಬಿಂಜಲಭಾವಿ</v>
+      </c>
+      <c r="B217" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>ಬಿಜ್ಜರಗಿ</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>ಬೀಳಗಿ</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>ಬೂದಿಹಾಳ</v>
+      </c>
+      <c r="B220" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C220" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D220" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E220">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>ಬೂದಿಹಾಳ ಪಿ ಟಿ</v>
+      </c>
+      <c r="B221" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>ಬೂಯ್ಯಾರ</v>
+      </c>
+      <c r="B222" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C222" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D222" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E222">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>ಬೆಕಿನಾಳ</v>
+      </c>
+      <c r="B223" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>ಬೆಂಗಳೂರ</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>ಬೆನಕನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B225" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C225" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D225" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>ಬೆನಕೊಟಗಿ</v>
+      </c>
+      <c r="B226" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>ಬೆವೂರ</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>ಬೆಳಗಾಂವಿ</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>ಬೇಲೂರ</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>ಬೊಳೆಗಾಂವ</v>
+      </c>
+      <c r="B230" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C230" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D230" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>ಬೋರಗಿ</v>
+      </c>
+      <c r="B231" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>ಬ್ಯಾಕೋಡ</v>
+      </c>
+      <c r="B232" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>ಬ್ಯಾಡಗಿಹಾಳ</v>
+      </c>
+      <c r="B233" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>ಬ್ರಹ್ಮದೇವರಮಡು</v>
+      </c>
+      <c r="B234" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>ಭಂಟನೂರ</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>ಭತಗುಣಕಿ</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C236" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D236" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E236">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>ಭೈರುಣಗಿ</v>
+      </c>
+      <c r="B237" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C237" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D237" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E237">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>ಮಖಣಾಪೂರ</v>
+      </c>
+      <c r="B238" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C238" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D238" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E238">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>ಮಂಗಳೂರ</v>
+      </c>
+      <c r="B239" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>ಮಡ್ಡಿಮಣ್ಣೂರ</v>
+      </c>
+      <c r="B240" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C240" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D240" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>ಮಡ್ನಳ್ಳಿ</v>
+      </c>
+      <c r="B241" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>ಮಣಂಕಲಗಿ</v>
+      </c>
+      <c r="B242" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C242" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D242" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E242">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>ಮಣ್ಣೂರ</v>
+      </c>
+      <c r="B243" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>ಮದರಿ</v>
+      </c>
+      <c r="B244" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>ಮಂದ್ರುಪ</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>ಮನಗೂಳಿ</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>ಮನ್ನಾಪೂರ</v>
+      </c>
+      <c r="B247" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>ಮರಗೂರ</v>
+      </c>
+      <c r="B248" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C248" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D248" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E248">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>ಮಲಘಾಣ</v>
+      </c>
+      <c r="B249" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>ಮಲ್ಕನ ದೇವರ ಹಟ್ಟಿ</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>ಮಸಳಿ ಕೆ ಡಿ</v>
+      </c>
+      <c r="B251" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C251" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D251" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E251">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>ಮಸಳಿ ಬಿ ಕೆ</v>
+      </c>
+      <c r="B252" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C252" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D252" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E252">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>ಮಾಗಣಗೇರಿ</v>
+      </c>
+      <c r="B253" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>ಮಾಡಬಾಳ</v>
+      </c>
+      <c r="B254" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>ಮಾಡ್ಯಾಳ</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>ಮಾರ್ಸನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B256" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C256" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D256" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E256">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>ಮಾವಿನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B257" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C257" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D257" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E257">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>ಮಿಂಚನಾಳ</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>ಮಿರಗಿ</v>
+      </c>
+      <c r="B259" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C259" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D259" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E259">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>ಮುದ್ದೇಬಿಹಾಳ</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>ಮುರಡಿ</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>ಮುಳವಾಡ</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>ಮುಳಸಾವಳಗಿ</v>
+      </c>
+      <c r="B263" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C263" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D263" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>ಮೈಲಾರ</v>
+      </c>
+      <c r="B264" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C264" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D264" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E264">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>ಮೈಸೂರ</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>ಮೋರಟಗಿ</v>
+      </c>
+      <c r="B266" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>ಯಂಕಂಚಿ</v>
+      </c>
+      <c r="B267" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>ಯರಗಲ್</v>
+      </c>
+      <c r="B268" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>ಯರಗಲ್ ಬಿ ಕ</v>
+      </c>
+      <c r="B269" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>ಯಲಗೋಡ</v>
+      </c>
+      <c r="B270" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>ಯಾಳವಾರ</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ರಬಕವಿ</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>ರಾಜನಾಳ</v>
+      </c>
+      <c r="B273" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C273" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D273" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>ರಾಮತಿರ್ಥ ಎಲ್ ಟಿ</v>
+      </c>
+      <c r="B274" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C274" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D274" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>ರಾಮನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B275" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>ರಾಮಪೂರ</v>
+      </c>
+      <c r="B276" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>ರಾಮಪೂರ ಪಿ ಎ</v>
+      </c>
+      <c r="B277" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>ರೇವತಗಾಂವ</v>
+      </c>
+      <c r="B278" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C278" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D278" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E278">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>ರೊರಟ್ಟಿ</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>ರೋಡಗಿ</v>
+      </c>
+      <c r="B280" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C280" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D280" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E280">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>ಲಚ್ಯಾಣ</v>
+      </c>
+      <c r="B281" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C281" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D281" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E281">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>ಲಾಳಸಂಗಿ</v>
+      </c>
+      <c r="B282" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C282" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D282" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E282">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>ಲಿಂಗದಳ್ಳಿ</v>
+      </c>
+      <c r="B283" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C283" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D283" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E283">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>ಲಿಂಗಾಪೂರ</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>ಲೋಣಿ ಕೆ ಡಿ</v>
+      </c>
+      <c r="B285" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C285" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D285" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E285">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>ಲೋಣಿ ಬಿ ಕೆ</v>
+      </c>
+      <c r="B286" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C286" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D286" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>ವಣಕಿಹಾಳ</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>ವರ್ಕಾನಳ್ಳಿ</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>ವಾಡೆ</v>
+      </c>
+      <c r="B289" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C289" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D289" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E289">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>ವಿಭೂತಿಹಳ್ಳಿ</v>
+      </c>
+      <c r="B291" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>ಶಂಬೇವಾಡ</v>
+      </c>
+      <c r="B292" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>ಶಿಗಣಾಪೂರ</v>
+      </c>
+      <c r="B293" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C293" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D293" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E293">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>ಶಿಂಗನಳ್ಳಿ</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>ಶಿರಕನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B295" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C295" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D295" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>ಶಿರಗೂರ ಇನಾಂ</v>
+      </c>
+      <c r="B296" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C296" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D296" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E296">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>ಶಿರಗೂರ ಖಾಲ್ಸಾ</v>
+      </c>
+      <c r="B297" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C297" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D297" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E297">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>ಶಿರಡೋಣ</v>
+      </c>
+      <c r="B298" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C298" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D298" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E298">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>ಶಿರನಾಳ</v>
+      </c>
+      <c r="B299" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C299" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D299" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E299">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>ಶಿರಶ್ಯಾಡ</v>
+      </c>
+      <c r="B300" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C300" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D300" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E300">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>ಶಿರಸಗಿ</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>ಶಿರೂರ</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>ಶಿವಣಗಿ</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>ಶಿವಪೂರ ಕೆ ಡಿ</v>
+      </c>
+      <c r="B304" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C304" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D304" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E304">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>ಶಿವಪೂರ ಬಿಕೆ</v>
+      </c>
+      <c r="B305" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C305" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D305" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>ಶೇಷಗಿರಿ</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>ಸಂಗೋಗಿ</v>
+      </c>
+      <c r="B307" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C307" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D307" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E307">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>ಸಾತಪೂರ</v>
+      </c>
+      <c r="B308" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C308" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D308" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E308">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>ಸಾತಲಗಾಂವ</v>
+      </c>
+      <c r="B309" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C309" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D309" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E309">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>ಸಾತಲಗಾಂವ ಪಿ ಐ</v>
+      </c>
+      <c r="B310" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C310" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D310" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E310">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>ಸಾತಲಗಾಂವ ಪಿ ಬಿ</v>
+      </c>
+      <c r="B311" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C311" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D311" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E311">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>ಸಾತಿಹಾಳ</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>ಸಾರವಾಡ</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>ಸಾಲೋಟಗಿ</v>
+      </c>
+      <c r="B314" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C314" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D314" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E314">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>ಸಾವಳಸಂಗ</v>
+      </c>
+      <c r="B315" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C315" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D315" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E315">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>ಸಾಸಾಬಾಳ</v>
+      </c>
+      <c r="B316" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>ಸಾಸ್ತಾನ (ಉಡಪಿ ತಾಲೂಕ, ದ.ಕ.)</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>ಸಿಂದಗಿ</v>
+      </c>
+      <c r="B318" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>ಸುಂಗಠಾಣ</v>
+      </c>
+      <c r="B319" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>ಸುರಗಿಹಳ್ಳಿ</v>
+      </c>
+      <c r="B320" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C320" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D320" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>ಸೊನಕನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B321" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C321" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D321" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E321">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>ಸೊನ್ನ</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>ಸೊನ್ನಗಿ</v>
+      </c>
+      <c r="B323" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>ಸೋಮಜಾಳ</v>
+      </c>
+      <c r="B324" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>ಸೋಮಪುರ</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>ಸೋಲಾಪೂರ</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>ಹಂಗರಗಿ</v>
+      </c>
+      <c r="B327" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>ಹಂಚನಾಳ</v>
+      </c>
+      <c r="B328" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C328" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D328" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E328">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ಹಚ್ಯಾಳ</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C329" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D329" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ಹಂಜಗಿ</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C330" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D330" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E330">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>ಹಡಲಸಂಗ</v>
+      </c>
+      <c r="B331" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C331" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D331" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E331">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>ಹತ್ತಳ್ಳಿ</v>
+      </c>
+      <c r="B332" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C332" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D332" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>ಹಂದಿಗನೂರ</v>
+      </c>
+      <c r="B333" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>ಹರನಾಳ</v>
+      </c>
+      <c r="B334" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C334" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D334" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>ಹಲಗಲಿ</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
         <v>ಹಲಸಂಗಿ</v>
       </c>
-      <c r="B27" t="str">
-        <v>ಹಲಸಂಗಿ ಸರ್ಕಲ</v>
-      </c>
-      <c r="C27" t="str">
-        <v>ಚಡಚಣ</v>
-      </c>
-      <c r="D27" t="str">
-        <v>ವಿಜಯಪುರ</v>
-      </c>
-      <c r="E27" t="str">
-        <v>586205</v>
-      </c>
-      <c r="F27" t="str">
-        <v>ಸುನೀಲ ಜೋಶಿ</v>
-      </c>
-      <c r="G27" t="str">
-        <v>9845011232</v>
+      <c r="B336" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C336" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D336" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E336">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>ಹವಳಗಿ</v>
+      </c>
+      <c r="B337" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>ಹಳಗುಣಕಿ</v>
+      </c>
+      <c r="B338" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C338" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D338" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E338">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>ಹಾಲಹಳ್ಳಿ</v>
+      </c>
+      <c r="B339" t="str">
+        <v>ಚಡಚಣ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C339" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D339" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E339">
+        <v>586204</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>ಹಾವಿನಾಳ</v>
+      </c>
+      <c r="B340" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C340" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D340" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>ಹಾಳಗುಂಡಕನಾಳ</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>ಹಿಕ್ಕಣಗುತ್ತಿ</v>
+      </c>
+      <c r="B342" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>ಹಿಂಗಣಿ</v>
+      </c>
+      <c r="B343" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C343" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D343" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E343">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>ಹಿಟ್ನಳ್ಳಿ</v>
+      </c>
+      <c r="B344" t="str">
+        <v>ತಾಂಬಾ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C344" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D344" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>ಹಿರೇಬೇವನೂರ</v>
+      </c>
+      <c r="B345" t="str">
+        <v>ಇಂಡಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C345" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D345" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E345">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>ಹಿರೇಮಸಳಿ</v>
+      </c>
+      <c r="B346" t="str">
+        <v>ಸಾಲೋಟಗಿ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C346" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D346" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E346">
+        <v>586217</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>ಹಿರೇರೂಗಿ</v>
+      </c>
+      <c r="B347" t="str">
+        <v>ಇಂಡಿ ಸ್ಟೇಶನ್‌ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C347" t="str">
+        <v>ಇಂಡಿ</v>
+      </c>
+      <c r="D347" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E347">
+        <v>586209</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>ಹೀರೆ ಮಣ್ಣೂರ</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>ಹುನಗುಂದ</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>ಹುಬನೂರ</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>ಹುಬ್ಬಳ್ಳಿ</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>ಹೂವಿನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B352" t="str">
+        <v>ಆಲಮೇಲ - ಸಿಂದಗಿ - ದೇವರಹಿಪ್ಪರಗಿ</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>ಹೊನಗನಹಳ್ಳಿ</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>ಹೊನ್ನಳ್ಳಿ</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>ಹೊನ್ನುಟಗಿ</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>ಹೊರ್ತಿ</v>
+      </c>
+      <c r="B356" t="str">
+        <v>ಧೂಳಖೇಡ ಸರ್ಕಲ</v>
+      </c>
+      <c r="C356" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D356" t="str">
+        <v>ವಿಜಯಪುರ</v>
+      </c>
+      <c r="E356">
+        <v>586207</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>ಹೊಳೆ ಹಂಗರಗಿ</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Post</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>ಹೋಳಿಸಂಖ</v>
+      </c>
+      <c r="B358" t="str">
+        <v>ಕೆರೂರ</v>
+      </c>
+      <c r="C358" t="str">
+        <v>ಚಡಚಣ</v>
+      </c>
+      <c r="D358" t="str">
+        <v>ವಿಜಯಪುರ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G358"/>
   </ignoredErrors>
 </worksheet>
 </file>